--- a/data/trans_camb/P0902-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,87</t>
+          <t>4,43; 11,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,6</t>
+          <t>1,69; 8,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 16,5</t>
+          <t>7,71; 16,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,42</t>
+          <t>8,34; 15,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 15,91</t>
+          <t>7,18; 15,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 22,16</t>
+          <t>14,98; 22,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,55</t>
+          <t>7,96; 13,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,66</t>
+          <t>6,07; 11,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 18,9</t>
+          <t>13,7; 19,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,41; 75,53</t>
+          <t>25,78; 79,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 60,95</t>
+          <t>9,38; 61,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 118,17</t>
+          <t>43,9; 115,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 72,13</t>
+          <t>33,47; 70,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 72,56</t>
+          <t>29,94; 70,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,77; 101,84</t>
+          <t>59,73; 102,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,37; 66,83</t>
+          <t>37,6; 70,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,57; 62,02</t>
+          <t>28,81; 59,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,66; 101,47</t>
+          <t>63,92; 102,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,74</t>
+          <t>-0,21; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,86</t>
+          <t>-0,31; 2,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,64</t>
+          <t>1,64; 6,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>-0,08; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,52</t>
+          <t>0,27; 4,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,62</t>
+          <t>-0,21; 5,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,92</t>
+          <t>0,32; 2,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,05</t>
+          <t>0,57; 3,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,57</t>
+          <t>1,71; 5,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 64,75</t>
+          <t>-4,42; 64,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 67,88</t>
+          <t>-5,01; 64,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 149,5</t>
+          <t>32,09; 148,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 50,14</t>
+          <t>-0,52; 50,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 54,32</t>
+          <t>3,32; 51,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 67,87</t>
+          <t>0,14; 68,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 45,62</t>
+          <t>3,66; 43,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 47,41</t>
+          <t>7,52; 47,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 86,34</t>
+          <t>22,87; 90,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,78</t>
+          <t>-1,14; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,32</t>
+          <t>-2,06; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,25</t>
+          <t>0,6; 6,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,96</t>
+          <t>-4,36; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,41</t>
+          <t>-3,0; 4,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,69</t>
+          <t>-2,33; 3,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,65</t>
+          <t>-1,83; 3,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,38</t>
+          <t>-1,53; 2,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,21</t>
+          <t>0,12; 4,29</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 167,9</t>
+          <t>-24,21; 170,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 107,36</t>
+          <t>-37,74; 122,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 210,98</t>
+          <t>6,57; 210,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 44,33</t>
+          <t>-43,94; 47,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 70,42</t>
+          <t>-29,82; 71,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 59,11</t>
+          <t>-22,94; 62,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 52,35</t>
+          <t>-26,11; 61,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 67,88</t>
+          <t>-21,68; 57,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 85,8</t>
+          <t>0,98; 86,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,28</t>
+          <t>1,51; 4,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,47</t>
+          <t>-0,25; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,44</t>
+          <t>0,83; 5,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,12</t>
+          <t>3,38; 6,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,77</t>
+          <t>1,28; 4,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,25</t>
+          <t>0,05; 5,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,35</t>
+          <t>2,89; 5,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,2</t>
+          <t>0,94; 3,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,08</t>
+          <t>1,53; 5,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,58; 57,62</t>
+          <t>17,78; 61,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 33,42</t>
+          <t>-2,74; 34,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,36; 72,16</t>
+          <t>12,2; 71,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,78; 52,46</t>
+          <t>21,68; 50,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,99; 34,74</t>
+          <t>8,73; 35,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 37,69</t>
+          <t>1,37; 39,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,97; 48,98</t>
+          <t>24,0; 47,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,9; 28,77</t>
+          <t>7,8; 30,2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,81; 46,18</t>
+          <t>12,97; 46,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0902-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,66</t>
+          <t>18,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,22</t>
+          <t>15,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,43</t>
+          <t>4,42; 11,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,88</t>
+          <t>1,45; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 16,23</t>
+          <t>6,65; 14,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 15,27</t>
+          <t>8,32; 15,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 15,39</t>
+          <t>7,72; 15,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,98; 22,39</t>
+          <t>14,44; 22,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 13,16</t>
+          <t>7,85; 12,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 11,3</t>
+          <t>5,71; 11,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,17</t>
+          <t>13,01; 17,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,78; 79,7</t>
+          <t>26,14; 87,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 61,99</t>
+          <t>7,63; 63,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,9; 115,15</t>
+          <t>38,91; 105,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,47; 70,55</t>
+          <t>32,53; 72,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,94; 70,27</t>
+          <t>30,62; 69,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,73; 102,83</t>
+          <t>56,72; 100,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,6; 70,04</t>
+          <t>37,44; 68,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,81; 59,18</t>
+          <t>27,66; 60,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,92; 102,6</t>
+          <t>61,35; 94,83</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>5,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,7</t>
+          <t>-0,42; 2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,71</t>
+          <t>-0,18; 2,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,52</t>
+          <t>4,04; 7,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,13</t>
+          <t>0,13; 4,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,24</t>
+          <t>0,27; 4,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,69</t>
+          <t>3,41; 7,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,77</t>
+          <t>0,38; 3,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,07</t>
+          <t>0,48; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,73</t>
+          <t>4,31; 6,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>112,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 64,75</t>
+          <t>-7,0; 62,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 64,56</t>
+          <t>-3,4; 67,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,09; 148,16</t>
+          <t>68,44; 180,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 50,69</t>
+          <t>0,1; 50,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 51,6</t>
+          <t>1,21; 53,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 68,89</t>
+          <t>31,99; 89,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 43,53</t>
+          <t>4,86; 46,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 47,38</t>
+          <t>6,49; 47,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 90,02</t>
+          <t>56,05; 109,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,02</t>
+          <t>-0,89; 5,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,46</t>
+          <t>-1,92; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,09</t>
+          <t>0,82; 6,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 3,03</t>
+          <t>-4,2; 2,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,52</t>
+          <t>-3,27; 4,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,9</t>
+          <t>-2,06; 4,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,19</t>
+          <t>-1,71; 2,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,9</t>
+          <t>-1,29; 3,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,29</t>
+          <t>0,38; 4,71</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 170,55</t>
+          <t>-20,44; 173,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 122,29</t>
+          <t>-36,41; 120,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 210,65</t>
+          <t>10,05; 196,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 47,19</t>
+          <t>-44,09; 43,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 71,42</t>
+          <t>-31,86; 70,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 62,71</t>
+          <t>-20,86; 71,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 61,82</t>
+          <t>-23,39; 61,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,68; 57,79</t>
+          <t>-18,91; 62,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 86,26</t>
+          <t>4,06; 94,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>4,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,51</t>
+          <t>1,32; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,55</t>
+          <t>-0,43; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,39</t>
+          <t>2,8; 5,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,95</t>
+          <t>3,42; 7,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,93</t>
+          <t>1,35; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,43</t>
+          <t>3,33; 6,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,17</t>
+          <t>2,89; 5,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,29</t>
+          <t>0,92; 3,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,1</t>
+          <t>3,61; 5,88</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,78; 61,23</t>
+          <t>14,71; 58,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 34,23</t>
+          <t>-4,6; 32,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,2; 71,57</t>
+          <t>31,65; 76,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,68; 50,94</t>
+          <t>21,76; 50,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 35,21</t>
+          <t>8,01; 35,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 39,72</t>
+          <t>21,25; 48,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,0; 47,79</t>
+          <t>24,6; 48,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,8; 30,2</t>
+          <t>7,72; 29,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 46,61</t>
+          <t>29,76; 54,17</t>
         </is>
       </c>
     </row>
